--- a/samples/sample_sales.xlsx
+++ b/samples/sample_sales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Visual Studios Repos\Chaman\RPA_BOT\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4567A53-6E28-4B94-A4C3-6109E46F11F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18239DF5-E294-42A2-8480-A98E9E3776F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Sales Type</t>
   </si>
@@ -52,38 +52,35 @@
     <t>Invoice Filename</t>
   </si>
   <si>
+    <t>40040000</t>
+  </si>
+  <si>
+    <t>List of End Products</t>
+  </si>
+  <si>
     <t>Domestic</t>
   </si>
   <si>
-    <t>05/04/2026</t>
-  </si>
-  <si>
-    <t>SALE-001</t>
-  </si>
-  <si>
-    <t>EINV-001</t>
-  </si>
-  <si>
-    <t>Sample Buyer Industries</t>
-  </si>
-  <si>
-    <t>40040000</t>
-  </si>
-  <si>
-    <t>Sample Industrial Area, Pune, Maharashtra</t>
-  </si>
-  <si>
-    <t>SALE-001.pdf</t>
-  </si>
-  <si>
-    <t>Price of Product</t>
+    <t>31/05/2026</t>
+  </si>
+  <si>
+    <t>Rebirth Sales</t>
+  </si>
+  <si>
+    <t>A-12 G.T.KARNAL ROAD INDUSTRIAL AREA AZADPUR AZADPUR 110033 DELHI</t>
+  </si>
+  <si>
+    <t>45 REBIRTH.pdf</t>
+  </si>
+  <si>
+    <t>pyrolysis oil or char:batch-2.250</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +92,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -122,9 +125,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,9 +442,9 @@
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="36" customWidth="1"/>
-    <col min="9" max="9" width="29" customWidth="1"/>
-    <col min="10" max="10" width="44" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="9" max="9" width="44" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -468,42 +473,42 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
         <v>13</v>
+      </c>
+      <c r="C2">
+        <v>45</v>
+      </c>
+      <c r="D2" s="3">
+        <v>142517486902058</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>93750</v>
+      </c>
+      <c r="H2">
+        <v>2250</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2">
-        <v>75000</v>
-      </c>
-      <c r="H2">
-        <v>8000</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
@@ -514,5 +519,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>